--- a/data/sensors/inertial-sensors.xlsx
+++ b/data/sensors/inertial-sensors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\react\dielcom\dielcom\data\sensors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9A4476-DDC4-4993-A5EB-8472FFBB13FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30030F05-58A4-43D2-A451-D6E8E0220A64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="25065" windowHeight="12675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkyMEMS IMU" sheetId="1" r:id="rId1"/>
@@ -511,10 +511,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>52</v>
@@ -543,10 +543,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
@@ -575,10 +575,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -607,10 +607,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>15</v>
@@ -639,10 +639,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -671,10 +671,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -703,10 +703,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
@@ -735,10 +735,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>15</v>
@@ -767,10 +767,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>46</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
